--- a/CastleHero_Table/Rate_Table.xlsx
+++ b/CastleHero_Table/Rate_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\CH_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0C8D62-4775-4E4A-8E1F-8AE44DE39973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB199E7E-614D-4DF7-8A78-2F26963D68C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7400" yWindow="1230" windowWidth="30670" windowHeight="19010" xr2:uid="{FC61C1C4-26C9-4266-8D7F-4500AC9D7DA5}"/>
+    <workbookView xWindow="7050" yWindow="1280" windowWidth="30700" windowHeight="19010" xr2:uid="{FC61C1C4-26C9-4266-8D7F-4500AC9D7DA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,42 +36,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Rate_Lv</t>
-  </si>
-  <si>
-    <t>승급 레벨</t>
   </si>
   <si>
     <t>Rate_Soul</t>
   </si>
   <si>
-    <t>승급 필요 영혼 수</t>
-  </si>
-  <si>
     <t>Rate_Gold _Normal</t>
-  </si>
-  <si>
-    <t>일반 등급 승급 필요 골드</t>
   </si>
   <si>
     <t>Rate_Gold _Rare</t>
   </si>
   <si>
-    <t>레어 등급 승급 필요 골드</t>
-  </si>
-  <si>
     <t>Rate_Gold _Epic</t>
   </si>
   <si>
-    <t>에픽 등급 승급 필요 골드</t>
-  </si>
-  <si>
     <t>Rate_Gold _Legend</t>
-  </si>
-  <si>
-    <t>전설 등급 승급 필요 골드</t>
   </si>
 </sst>
 </file>
@@ -484,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{976F59F7-C029-4286-BBA3-A780DC0157BA}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -494,163 +476,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="B2" s="1">
         <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>100</v>
+      </c>
+      <c r="D2" s="1">
+        <v>200</v>
+      </c>
+      <c r="E2" s="1">
+        <v>300</v>
+      </c>
+      <c r="F2" s="1">
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1">
-        <v>100</v>
+        <f>C2*5</f>
+        <v>500</v>
       </c>
       <c r="D3" s="1">
-        <v>200</v>
+        <f t="shared" ref="D3:F6" si="0">D2*5</f>
+        <v>1000</v>
       </c>
       <c r="E3" s="1">
-        <v>300</v>
+        <f t="shared" si="0"/>
+        <v>1500</v>
       </c>
       <c r="F3" s="1">
-        <v>400</v>
+        <f t="shared" si="0"/>
+        <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" s="1">
-        <f>C3*5</f>
-        <v>500</v>
+        <f t="shared" ref="C4:C6" si="1">C3*5</f>
+        <v>2500</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" ref="D4:F7" si="0">D3*5</f>
-        <v>1000</v>
+        <f t="shared" si="0"/>
+        <v>5000</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" si="0"/>
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" ref="C5:C7" si="1">C4*5</f>
-        <v>2500</v>
+        <f t="shared" si="1"/>
+        <v>12500</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>7500</v>
+        <v>37500</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>12500</v>
+        <v>62500</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>25000</v>
+        <v>125000</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>37500</v>
+        <v>187500</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="0"/>
-        <v>50000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1">
-        <v>500</v>
-      </c>
-      <c r="C7" s="1">
-        <f t="shared" si="1"/>
-        <v>62500</v>
-      </c>
-      <c r="D7" s="1">
-        <f t="shared" si="0"/>
-        <v>125000</v>
-      </c>
-      <c r="E7" s="1">
-        <f t="shared" si="0"/>
-        <v>187500</v>
-      </c>
-      <c r="F7" s="1">
-        <f t="shared" si="0"/>
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="1">
         <v>5</v>
       </c>
     </row>
